--- a/docs/PIMS_DASHBOARD_System_Specification_VN.xlsx
+++ b/docs/PIMS_DASHBOARD_System_Specification_VN.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD542DA-DE1B-475A-BA94-A70C8250C272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="Ma_Tran_Nguon_Du_Lieu" sheetId="1" r:id="rId1"/>
-    <sheet name="Quy_Cach_10_JSP_API" sheetId="2" r:id="rId2"/>
-    <sheet name="Quy_Cach_Mau_Excel_Upload" sheetId="3" r:id="rId3"/>
-    <sheet name="Huong_Dan_Nhap_Tay_Quan_Tri" sheetId="4" r:id="rId4"/>
+    <sheet sheetId="1" name="Ma_Tran_Nguon_Du_Lieu" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Quy_Cach_10_JSP_API" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Quy_Cach_Mau_Excel_Upload" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Huong_Dan_Nhap_Tay_Quan_Tri" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Ma_Tran_Chi_So_Lineage" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="579">
   <si>
     <t>MA TRẬN NGUỒN DỮ LIỆU VÀ ĐẶC TẢ ĐỐI CHIẾU HỆ THỐNG PIMS-DASHBOARD</t>
   </si>
@@ -1467,50 +1467,349 @@
   </si>
   <si>
     <t>Allows executive finance to test sensitivity analysis or adjust internal reporting rate.</t>
+  </si>
+  <si>
+    <t>Ma Trận Ánh Xạ Chỉ Số &amp; Nguồn Gốc Dữ Liệu (Data Lineage)</t>
+  </si>
+  <si>
+    <t>Màn hình</t>
+  </si>
+  <si>
+    <t>Tên chỉ số</t>
+  </si>
+  <si>
+    <t>Loại nhập liệu</t>
+  </si>
+  <si>
+    <t>Menu PIMSVINA</t>
+  </si>
+  <si>
+    <t>Tên UI PIMSVINA</t>
+  </si>
+  <si>
+    <t>Dashboard Toàn Công Ty - Tổng Quan Chính</t>
+  </si>
+  <si>
+    <t>Doanh thu lũy kế năm (Kế hoạch / Thực tế / Tỷ lệ đạt)</t>
+  </si>
+  <si>
+    <t>Tải lên Excel</t>
+  </si>
+  <si>
+    <t>Monthly Management Performance Registration</t>
+  </si>
+  <si>
+    <t>Management Report Excel (Revenue line cumulative)</t>
+  </si>
+  <si>
+    <t>Lợi nhuận kinh doanh lũy kế năm (Kế hoạch / Thực tế / Tỷ lệ đạt)</t>
+  </si>
+  <si>
+    <t>Management Report Excel (Operating Profit line cumulative)</t>
+  </si>
+  <si>
+    <t>Doanh thu cả năm (Kế hoạch / Dự báo / Tỷ lệ đạt)</t>
+  </si>
+  <si>
+    <t>Management Report Excel (Full-Year Total)</t>
+  </si>
+  <si>
+    <t>Lợi nhuận kinh doanh cả năm (Kế hoạch / Dự báo / Tỷ lệ đạt)</t>
+  </si>
+  <si>
+    <t>Dashboard Toàn Công Ty - Biểu Đồ</t>
+  </si>
+  <si>
+    <t>Xu hướng doanh thu hàng tháng (Kế hoạch so với Thực tế/Dự báo)</t>
+  </si>
+  <si>
+    <t>Management Report Excel (Monthly Revenue)</t>
+  </si>
+  <si>
+    <t>Tình hình lãi lỗ hàng tháng (Lợi nhuận gộp, CP QLDN, LN kinh doanh)</t>
+  </si>
+  <si>
+    <t>Management Report Excel (P&amp;L lines)</t>
+  </si>
+  <si>
+    <t>Tình hình trúng thầu (Mục tiêu hợp đồng, Đã trúng thầu, Còn lại)</t>
+  </si>
+  <si>
+    <t>Management Report Excel (Orders/Contracts)</t>
+  </si>
+  <si>
+    <t>Dòng tiền công ty (Thu, Chi, Số dư ròng)</t>
+  </si>
+  <si>
+    <t>1. Site Fund Movement (Cash / Bank) / Cash Flow Sheet</t>
+  </si>
+  <si>
+    <t>Cash Flow Excel Upload</t>
+  </si>
+  <si>
+    <t>Dashboard Toàn Công Ty - Bảng &amp; Tổng Hợp</t>
+  </si>
+  <si>
+    <t>Bảng tổng hợp kết quả kinh doanh</t>
+  </si>
+  <si>
+    <t>Management Report Excel Sheet</t>
+  </si>
+  <si>
+    <t>Dashboard Toàn Công Ty - Nhận Xét</t>
+  </si>
+  <si>
+    <t>Nhận xét điều hành (Phân tích kết quả &amp; Triển vọng)</t>
+  </si>
+  <si>
+    <t>Nhập tay</t>
+  </si>
+  <si>
+    <t>Bottom Comment Panel (Edit &amp; Save)</t>
+  </si>
+  <si>
+    <t>Chi Tiết Dự Án Xây Dựng - Tab Khái Yếu</t>
+  </si>
+  <si>
+    <t>Giá trị hợp đồng (VND)</t>
+  </si>
+  <si>
+    <t>Đồng bộ ERP</t>
+  </si>
+  <si>
+    <t>Construction Overview Registration / Contract Summary</t>
+  </si>
+  <si>
+    <t>Total Contract Won Amount (TOTALCTRTWONAMT)</t>
+  </si>
+  <si>
+    <t>Thời gian thi công (Ngày bắt đầu &amp; kết thúc)</t>
+  </si>
+  <si>
+    <t>Construction Overview Registration &gt; Period</t>
+  </si>
+  <si>
+    <t>Actual Start (STCONSTDATE) ~ Sched. Completion (CMPLSCHDDATE)</t>
+  </si>
+  <si>
+    <t>Thông số dự án (Chủ đầu tư, Quy mô, Diện tích, Vị trí, Mục đích, Bảo hành, Tạm ứng)</t>
+  </si>
+  <si>
+    <t>Construction Overview Registration (Unregistered items)</t>
+  </si>
+  <si>
+    <t>Data Entry Tab &gt; 0. Overview Information</t>
+  </si>
+  <si>
+    <t>Ảnh phối cảnh / Ảnh trên không</t>
+  </si>
+  <si>
+    <t>Construction Overview Registration &gt; Aerial View</t>
+  </si>
+  <si>
+    <t>Aerial View Picture File (AIRVIEWPICPATH)</t>
+  </si>
+  <si>
+    <t>Chi Tiết Dự Án Xây Dựng - Tab Tiến Độ</t>
+  </si>
+  <si>
+    <t>Tiến độ thực tế hàng tháng (%)</t>
+  </si>
+  <si>
+    <t>Cost Progress Rate (%) / Execution Progress (Site)</t>
+  </si>
+  <si>
+    <t>Calculated progress rate based on monthly cost input</t>
+  </si>
+  <si>
+    <t>Tiến độ kế hoạch hàng tháng (%) &amp; Mốc tiến độ</t>
+  </si>
+  <si>
+    <t>N/A (Site Schedule Table)</t>
+  </si>
+  <si>
+    <t>Data Entry Tab &gt; 1. Monthly Progress / 2. Milestones (Excel Upload supported)</t>
+  </si>
+  <si>
+    <t>Ảnh tiến độ công trường hàng tháng</t>
+  </si>
+  <si>
+    <t>Monthly Construction Photo Registration</t>
+  </si>
+  <si>
+    <t>Monthly Photo List with Location/Trade Notes</t>
+  </si>
+  <si>
+    <t>Chi Tiết Dự Án Xây Dựng - Tab Doanh Thu/Lợi Nhuận</t>
+  </si>
+  <si>
+    <t>Doanh thu công trường hàng tháng (Kế hoạch / Thực tế / Dự báo)</t>
+  </si>
+  <si>
+    <t>Monthly Management Performance Registration / Excel</t>
+  </si>
+  <si>
+    <t>Site Monthly Revenue Column</t>
+  </si>
+  <si>
+    <t>Thiết lập tỷ lệ giá vốn (Đấu thầu, Thực hiện, Hoàn thành)</t>
+  </si>
+  <si>
+    <t>Execution Budget Proposal / Settlement Cost Ratio</t>
+  </si>
+  <si>
+    <t>Business Budget, Contract Amount, Gross Profit Ratio</t>
+  </si>
+  <si>
+    <t>Chi Tiết Dự Án Xây Dựng - Tab Thầu Phụ</t>
+  </si>
+  <si>
+    <t>Danh sách &amp; Giá trị hợp đồng thầu phụ (Ngân sách, NS thực hiện, Quyết toán HĐ, Tiến độ)</t>
+  </si>
+  <si>
+    <t>Execution Progress (Site) / Sub-Contract Detailed Bid / Resolution</t>
+  </si>
+  <si>
+    <t>Budget (A), Executed Budget, Resolved (B), Current Month, Cumulative (C), Exec Rate</t>
+  </si>
+  <si>
+    <t>Chi Tiết Dự Án Xây Dựng - Tab Chi Phí</t>
+  </si>
+  <si>
+    <t>Thực hiện ngân sách theo CBS (CP trực tiếp, CP gián tiếp, Dự phòng)</t>
+  </si>
+  <si>
+    <t>Execution Budget Proposal &gt; Cost Breakdown</t>
+  </si>
+  <si>
+    <t>Budget &amp; Incurred Cost by Standard CBS</t>
+  </si>
+  <si>
+    <t>Kế hoạch chi phí hàng tháng &amp; Phân loại theo nhóm công việc</t>
+  </si>
+  <si>
+    <t>N/A (Site Cost Incurrence Plan)</t>
+  </si>
+  <si>
+    <t>Data Entry Tab &gt; 4. Cost Plan/Actual by Work Type</t>
+  </si>
+  <si>
+    <t>Chi Tiết Dự Án Xây Dựng - Tab Dòng Tiền</t>
+  </si>
+  <si>
+    <t>Dòng tiền vào/ra &amp; Số dư tiền mặt dự án</t>
+  </si>
+  <si>
+    <t>1. Site Fund Movement (Cash / Bank) / Transactions</t>
+  </si>
+  <si>
+    <t>Income / Withdrawal / Opening Balance</t>
+  </si>
+  <si>
+    <t>Chi Tiết Dự Án Dịch Vụ - Khái Yếu &amp; Doanh Thu</t>
+  </si>
+  <si>
+    <t>Hợp đồng dịch vụ &amp; Phạm vi công việc</t>
+  </si>
+  <si>
+    <t>Service Contract / Order Management</t>
+  </si>
+  <si>
+    <t>Data Entry Tab &gt; Service Overview (Period, Client, Scope, Payment Terms)</t>
+  </si>
+  <si>
+    <t>Chi Tiết Dự Án Dịch Vụ - Tab Doanh Thu &amp; Giá Vốn</t>
+  </si>
+  <si>
+    <t>Giá vốn kế toán &amp; Giá vốn thực hiện hàng tháng (Dịch vụ, WIP)</t>
+  </si>
+  <si>
+    <t>Monthly Management Performance / Service Cost</t>
+  </si>
+  <si>
+    <t>Data Entry Tab &gt; 3. Monthly Cost of Revenue</t>
+  </si>
+  <si>
+    <t>Quản Trị Hệ Thống - Đồng Bộ &amp; Nạp Dữ Liệu</t>
+  </si>
+  <si>
+    <t>Quản lý tỷ giá hối đoái (USD / VND / KRW)</t>
+  </si>
+  <si>
+    <t>Contract Exchange Rate / CHTB_EXCHANGE_RATIO</t>
+  </si>
+  <si>
+    <t>Dashboard Top FX Rate Editor Modal</t>
+  </si>
+  <si>
+    <t>Nạp file Excel báo cáo quản trị &amp; Khôi phục phiên bản trước</t>
+  </si>
+  <si>
+    <t>Upload Modal (Management Report Excel Parsing)</t>
+  </si>
+  <si>
+    <t>Đồng bộ tự động PIMSVINA (Xem trước &amp; Xác nhận)</t>
+  </si>
+  <si>
+    <t>ERP All Modules</t>
+  </si>
+  <si>
+    <t>Top 'PIMS Sync' button -&gt; Preview Popup -&gt; Confirm Apply</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FF1E3A8A"/>
       <sz val="14"/>
-      <color rgb="FF1E3A8A"/>
       <name val="Segoe UI"/>
     </font>
     <font>
       <i/>
+      <color rgb="FF64748B"/>
       <sz val="10"/>
-      <color rgb="FF64748B"/>
       <name val="Segoe UI"/>
     </font>
     <font>
       <b/>
+      <color rgb="FF334155"/>
       <sz val="9"/>
-      <color rgb="FF334155"/>
       <name val="Segoe UI"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Segoe UI"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Segoe UI"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1A365D"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1547,8 +1846,13 @@
         <fgColor rgb="FFF3F4F6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF8FF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1571,11 +1875,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCBD5E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCBD5E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCBD5E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1604,6 +1923,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1942,9 +2270,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="31" customWidth="1"/>
@@ -1958,7 +2286,7 @@
     <col min="11" max="11" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="32.1" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1993,7 +2321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="20.1" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -2028,7 +2356,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="21.95" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -2063,7 +2391,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="27.95" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -2098,7 +2426,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -2133,7 +2461,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>2</v>
       </c>
@@ -2168,7 +2496,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>3</v>
       </c>
@@ -2203,7 +2531,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>4</v>
       </c>
@@ -2238,7 +2566,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>5</v>
       </c>
@@ -2273,7 +2601,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>6</v>
       </c>
@@ -2308,7 +2636,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>7</v>
       </c>
@@ -2343,7 +2671,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>8</v>
       </c>
@@ -2378,7 +2706,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>9</v>
       </c>
@@ -2413,7 +2741,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>10</v>
       </c>
@@ -2448,7 +2776,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>11</v>
       </c>
@@ -2483,7 +2811,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>12</v>
       </c>
@@ -2518,7 +2846,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>13</v>
       </c>
@@ -2553,7 +2881,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>14</v>
       </c>
@@ -2588,7 +2916,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>15</v>
       </c>
@@ -2623,7 +2951,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>16</v>
       </c>
@@ -2658,7 +2986,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>17</v>
       </c>
@@ -2693,7 +3021,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>18</v>
       </c>
@@ -2728,7 +3056,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>19</v>
       </c>
@@ -2763,7 +3091,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>20</v>
       </c>
@@ -2798,7 +3126,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>21</v>
       </c>
@@ -2833,7 +3161,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
         <v>22</v>
       </c>
@@ -2868,7 +3196,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>23</v>
       </c>
@@ -2903,7 +3231,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <v>24</v>
       </c>
@@ -2938,7 +3266,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>25</v>
       </c>
@@ -2973,7 +3301,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
         <v>26</v>
       </c>
@@ -3008,7 +3336,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>27</v>
       </c>
@@ -3043,7 +3371,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="7">
         <v>28</v>
       </c>
@@ -3078,7 +3406,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>29</v>
       </c>
@@ -3113,7 +3441,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
         <v>30</v>
       </c>
@@ -3148,7 +3476,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>31</v>
       </c>
@@ -3183,7 +3511,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
         <v>32</v>
       </c>
@@ -3218,7 +3546,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>33</v>
       </c>
@@ -3253,7 +3581,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <v>34</v>
       </c>
@@ -3288,7 +3616,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>35</v>
       </c>
@@ -3323,7 +3651,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <v>36</v>
       </c>
@@ -3358,7 +3686,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>37</v>
       </c>
@@ -3393,7 +3721,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="7">
         <v>38</v>
       </c>
@@ -3428,7 +3756,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>39</v>
       </c>
@@ -3463,7 +3791,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="7">
         <v>40</v>
       </c>
@@ -3500,14 +3828,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -3519,7 +3847,7 @@
     <col min="8" max="8" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>327</v>
       </c>
@@ -3545,7 +3873,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="20.1" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>329</v>
       </c>
@@ -3571,7 +3899,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="27.95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>331</v>
       </c>
@@ -3597,7 +3925,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>339</v>
       </c>
@@ -3623,7 +3951,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>347</v>
       </c>
@@ -3649,7 +3977,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>355</v>
       </c>
@@ -3675,7 +4003,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>362</v>
       </c>
@@ -3701,7 +4029,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>368</v>
       </c>
@@ -3727,7 +4055,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>373</v>
       </c>
@@ -3753,7 +4081,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>380</v>
       </c>
@@ -3779,7 +4107,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>386</v>
       </c>
@@ -3805,7 +4133,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>392</v>
       </c>
@@ -3831,7 +4159,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>400</v>
       </c>
@@ -3859,14 +4187,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="3" width="28" customWidth="1"/>
@@ -3876,7 +4204,7 @@
     <col min="7" max="7" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>408</v>
       </c>
@@ -3899,7 +4227,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="20.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>410</v>
       </c>
@@ -3922,7 +4250,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="27.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>412</v>
       </c>
@@ -3945,7 +4273,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>419</v>
       </c>
@@ -3968,7 +4296,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>426</v>
       </c>
@@ -3991,7 +4319,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>433</v>
       </c>
@@ -4016,14 +4344,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -4033,7 +4361,7 @@
     <col min="6" max="6" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>440</v>
       </c>
@@ -4053,7 +4381,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="20.1" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>442</v>
       </c>
@@ -4073,7 +4401,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="27.95" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>444</v>
       </c>
@@ -4093,7 +4421,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>450</v>
       </c>
@@ -4113,7 +4441,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>316</v>
       </c>
@@ -4133,7 +4461,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>316</v>
       </c>
@@ -4153,7 +4481,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>316</v>
       </c>
@@ -4173,7 +4501,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>471</v>
       </c>
@@ -4193,7 +4521,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>477</v>
       </c>
@@ -4215,6 +4543,528 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="5" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>484</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>487</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>489</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>490</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>489</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>494</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>489</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>496</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>489</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>498</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>499</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>500</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>499</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>502</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>499</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>504</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>499</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>506</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>507</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>509</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>510</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>512</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>513</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>514</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>516</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>517</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>518</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>519</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>516</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>518</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>516</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>514</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>525</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>516</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>527</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>518</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>528</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>530</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>531</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>518</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>530</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>534</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>514</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>535</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>530</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>537</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>518</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>538</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>540</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>542</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>540</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>518</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>545</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>547</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>548</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>518</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>549</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>551</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>552</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>518</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>553</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>551</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>555</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>514</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>556</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>558</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>559</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>518</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>560</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>562</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>563</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>514</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>564</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
+        <v>566</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>514</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>570</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>571</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>514</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>572</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>570</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>574</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>570</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>576</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>518</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>577</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>578</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>